--- a/CSV2ICS_Template.xlsx
+++ b/CSV2ICS_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$W$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,7 +36,24 @@
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00CC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -53,7 +70,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
+        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,15 +100,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,26 +480,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
@@ -490,14 +521,14 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>End Time</t>
@@ -540,17 +571,554 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Recurrence</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Recurrence End Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Recurrence Count</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Recurrence Interval</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Required Attendees</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Optional Attendees</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="n"/>
+      <c r="Q3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" s="3" t="n"/>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
+      <c r="U6" s="2" t="n"/>
+      <c r="V6" s="2" t="n"/>
+      <c r="W6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
+      <c r="Q7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" s="3" t="n"/>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="n"/>
+      <c r="U8" s="2" t="n"/>
+      <c r="V8" s="2" t="n"/>
+      <c r="W8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
+      <c r="Q9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" s="3" t="n"/>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="n"/>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="n"/>
+      <c r="U12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
+      <c r="W14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n"/>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n"/>
+      <c r="W15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
+      <c r="Q17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n"/>
+      <c r="V17" s="3" t="n"/>
+      <c r="W17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="2" t="n"/>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
+      <c r="W18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="3" t="n"/>
+      <c r="W19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="n"/>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+      <c r="W20" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:W1"/>
+  <dataValidations count="5">
+    <dataValidation sqref="F2:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CONFIRMED,TENTATIVE,CANCELLED"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"OPAQUE,TRANSPARENT"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"PUBLIC,PRIVATE,CONFIDENTIAL"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Daily,Weekly,Fortnightly,Monthly,Yearly,Weekday"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -558,44 +1126,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Example Values</t>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Accepted Values / Examples</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Event name/summary (required with Start Date)</t>
+          <t>Event title/summary</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -603,67 +1177,87 @@
           <t>Team Meeting, Birthday Party</t>
         </is>
       </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Event start date (required)</t>
+          <t>Event start date</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>29/01/2026, 01/29/2026, 2026-01-29</t>
+          <t>29/01/2026, 2026-01-29, 01/29/2026</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Event end date (optional if Duration used)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Start time (leave blank for all-day events)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>09:00, 2:30 PM, 14:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>End Date</t>
-        </is>
-      </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Event end date (optional, defaults to Start Date)</t>
+          <t>Start time (leave blank for all-day)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>09:00, 9:30 AM, 14:00</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>End Time</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>End time (optional)</t>
+          <t>End time</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -671,77 +1265,102 @@
           <t>17:00, 5:00 PM</t>
         </is>
       </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>All Day</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Mark as all-day event</t>
+          <t>Whether all-day event</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Yes, No, TRUE, FALSE</t>
+          <t>Yes, No</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Event venue or address</t>
+          <t>Venue or address</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Conference Room A, 10 Downing Street</t>
+          <t>Conference Room B, 10 Downing St</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Detailed notes about the event</t>
+          <t>Event details/notes</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Quarterly review with stakeholders</t>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Event category/tag</t>
+          <t>Event categories</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Work, Personal, Holiday</t>
+          <t>Work, Personal, Meeting</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -753,12 +1372,17 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>https://example.com/meeting</t>
+          <t>https://example.com</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -773,55 +1397,329 @@
           <t>CONFIRMED, TENTATIVE, CANCELLED</t>
         </is>
       </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Priority level (1=highest, 9=lowest)</t>
+          <t>Importance (0=undefined, 1=highest, 9=lowest)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1, 5, 9</t>
+          <t>0-9</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Transparency</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Free/busy indicator</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>OPAQUE (busy), TRANSPARENT (free)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Visibility/access level</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PUBLIC, PRIVATE, CONFIDENTIAL</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Reminder</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Alert before event starts</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>15 minutes, 1 hour, 1 day, None</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Minutes before event to alert</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>15, 60, 1440, or '2 hours', '1 day'</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Recurrence</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Repeating pattern</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Daily, Weekly, Monthly, Yearly, Fortnightly, Weekdays</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Repeat pattern</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Daily, Weekly, Monthly, Yearly, Fortnightly, Weekday</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Recurrence End Date</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>When recurring events stop</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Recurrence Count</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Number of occurrences</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>10, 52</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Recurrence Interval</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Gap between occurrences</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2 (=every 2 weeks/months)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Organizer</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Meeting organizer email</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>john@example.com</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Required Attendees</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Required attendee emails (;-separated)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>a@ex.com; b@ex.com</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Optional Attendees</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Optional attendee emails (;-separated)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>c@ex.com; d@ex.com</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Event length (alternative to End Date/Time)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>1 hour, 30 minutes, 1.5 hours</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Tips:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>• Only Title and Start Date are required. All other fields are optional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>• Select your date format on Page 1 of CSV2ICS to match your data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>• Default reminders can also be set on the Export page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>• Save as CSV (UTF-8) before importing. TSV (tab-delimited) is also supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>• Attendee emails should be separated by semicolons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>• Duration is used instead of End Date/Time when End Date is not provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>• Recurrence Count and End Date are mutually exclusive (RFC 5545).</t>
         </is>
       </c>
     </row>

--- a/CSV2ICS_Template.xlsx
+++ b/CSV2ICS_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Events'!$A$1:$X$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -506,6 +506,7 @@
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="30" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -622,6 +623,11 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Duration</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Timezone</t>
         </is>
       </c>
     </row>
@@ -649,6 +655,7 @@
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -674,6 +681,7 @@
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
       <c r="W3" s="3" t="n"/>
+      <c r="X3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -699,6 +707,7 @@
       <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="n"/>
       <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -724,6 +733,7 @@
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
       <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -749,6 +759,7 @@
       <c r="U6" s="2" t="n"/>
       <c r="V6" s="2" t="n"/>
       <c r="W6" s="2" t="n"/>
+      <c r="X6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -774,6 +785,7 @@
       <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="n"/>
+      <c r="X7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -799,6 +811,7 @@
       <c r="U8" s="2" t="n"/>
       <c r="V8" s="2" t="n"/>
       <c r="W8" s="2" t="n"/>
+      <c r="X8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -824,6 +837,7 @@
       <c r="U9" s="3" t="n"/>
       <c r="V9" s="3" t="n"/>
       <c r="W9" s="3" t="n"/>
+      <c r="X9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -849,6 +863,7 @@
       <c r="U10" s="2" t="n"/>
       <c r="V10" s="2" t="n"/>
       <c r="W10" s="2" t="n"/>
+      <c r="X10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -874,6 +889,7 @@
       <c r="U11" s="3" t="n"/>
       <c r="V11" s="3" t="n"/>
       <c r="W11" s="3" t="n"/>
+      <c r="X11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -899,6 +915,7 @@
       <c r="U12" s="2" t="n"/>
       <c r="V12" s="2" t="n"/>
       <c r="W12" s="2" t="n"/>
+      <c r="X12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -924,6 +941,7 @@
       <c r="U13" s="3" t="n"/>
       <c r="V13" s="3" t="n"/>
       <c r="W13" s="3" t="n"/>
+      <c r="X13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -949,6 +967,7 @@
       <c r="U14" s="2" t="n"/>
       <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="n"/>
+      <c r="X14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -974,6 +993,7 @@
       <c r="U15" s="3" t="n"/>
       <c r="V15" s="3" t="n"/>
       <c r="W15" s="3" t="n"/>
+      <c r="X15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -999,6 +1019,7 @@
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n"/>
       <c r="W16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -1024,6 +1045,7 @@
       <c r="U17" s="3" t="n"/>
       <c r="V17" s="3" t="n"/>
       <c r="W17" s="3" t="n"/>
+      <c r="X17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1049,6 +1071,7 @@
       <c r="U18" s="2" t="n"/>
       <c r="V18" s="2" t="n"/>
       <c r="W18" s="2" t="n"/>
+      <c r="X18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -1074,6 +1097,7 @@
       <c r="U19" s="3" t="n"/>
       <c r="V19" s="3" t="n"/>
       <c r="W19" s="3" t="n"/>
+      <c r="X19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1099,9 +1123,10 @@
       <c r="U20" s="2" t="n"/>
       <c r="V20" s="2" t="n"/>
       <c r="W20" s="2" t="n"/>
+      <c r="X20" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:X1"/>
   <dataValidations count="5">
     <dataValidation sqref="F2:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
@@ -1130,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1667,57 +1692,79 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Timezone</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>IANA timezone for this event</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Europe/London, America/New_York, Asia/Tokyo</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Tips:</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>• Only Title and Start Date are required. All other fields are optional.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>• Select your date format on Page 1 of CSV2ICS to match your data.</t>
+          <t>• Only Title and Start Date are required. All other fields are optional.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>• Default reminders can also be set on the Export page.</t>
+          <t>• Select your date format on Page 1 of CSV2ICS to match your data.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>• Save as CSV (UTF-8) before importing. TSV (tab-delimited) is also supported.</t>
+          <t>• Default reminders can also be set on the Export page.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>• Attendee emails should be separated by semicolons.</t>
+          <t>• Save as CSV (UTF-8) before importing. TSV (tab-delimited) is also supported.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>• Duration is used instead of End Date/Time when End Date is not provided.</t>
+          <t>• Attendee emails should be separated by semicolons.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>• Duration is used instead of End Date/Time when End Date is not provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>• Recurrence Count and End Date are mutually exclusive (RFC 5545).</t>
         </is>
